--- a/artfynd/A 11846-2024 artfynd.xlsx
+++ b/artfynd/A 11846-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680931</v>
+        <v>121680965</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579970</v>
+        <v>579973</v>
       </c>
       <c r="R2" t="n">
-        <v>6650477</v>
+        <v>6650480</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Josefine Kyhlström Swahn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680965</v>
+        <v>121680931</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579973</v>
+        <v>579970</v>
       </c>
       <c r="R3" t="n">
-        <v>6650480</v>
+        <v>6650477</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Josefine Kyhlström Swahn</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 11846-2024 artfynd.xlsx
+++ b/artfynd/A 11846-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680965</v>
+        <v>121680931</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579973</v>
+        <v>579970</v>
       </c>
       <c r="R2" t="n">
-        <v>6650480</v>
+        <v>6650477</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Josefine Kyhlström Swahn</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680931</v>
+        <v>121680965</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579970</v>
+        <v>579973</v>
       </c>
       <c r="R3" t="n">
-        <v>6650477</v>
+        <v>6650480</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Josefine Kyhlström Swahn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 11846-2024 artfynd.xlsx
+++ b/artfynd/A 11846-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680965</v>
+        <v>121680931</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579973</v>
+        <v>579970</v>
       </c>
       <c r="R2" t="n">
-        <v>6650480</v>
+        <v>6650477</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Josefine Kyhlström Swahn</t>
+          <t>Diana Rubene</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680931</v>
+        <v>121680965</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579970</v>
+        <v>579973</v>
       </c>
       <c r="R3" t="n">
-        <v>6650477</v>
+        <v>6650480</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -894,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Diana Rubene</t>
+          <t>Josefine Kyhlström Swahn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 11846-2024 artfynd.xlsx
+++ b/artfynd/A 11846-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121680931</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,8 +932,17 @@
           <t>Rejlers - Sala till Avesta</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121680965</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>